--- a/utils/monday_sprint_sprint_2025-5.xlsx
+++ b/utils/monday_sprint_sprint_2025-5.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1146" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="208">
   <si>
     <t>Ticket</t>
   </si>
@@ -204,6 +204,9 @@
     <t>10/02/2025</t>
   </si>
   <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
     <t>Semana 2</t>
   </si>
   <si>
@@ -483,7 +486,7 @@
     <t>15/10/2024</t>
   </si>
   <si>
-    <t>29/03/2026</t>
+    <t>24/03/2026</t>
   </si>
   <si>
     <t>Outubro</t>
@@ -619,9 +622,6 @@
   </si>
   <si>
     <t>Não definida</t>
-  </si>
-  <si>
-    <t>Semana 5</t>
   </si>
   <si>
     <t>Homologação</t>
@@ -1849,21 +1849,21 @@
         <v>62</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>35</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>15</v>
@@ -1875,10 +1875,10 @@
         <v>17</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>19</v>
@@ -1907,7 +1907,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>15</v>
@@ -1919,10 +1919,10 @@
         <v>17</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>19</v>
@@ -1943,7 +1943,7 @@
         <v>35</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>17</v>
@@ -1951,7 +1951,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>15</v>
@@ -1963,10 +1963,10 @@
         <v>17</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>19</v>
@@ -1995,7 +1995,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>15</v>
@@ -2007,10 +2007,10 @@
         <v>17</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>19</v>
@@ -2039,7 +2039,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>15</v>
@@ -2083,7 +2083,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>15</v>
@@ -2095,10 +2095,10 @@
         <v>17</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>19</v>
@@ -2127,7 +2127,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>15</v>
@@ -2139,10 +2139,10 @@
         <v>17</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>19</v>
@@ -2171,7 +2171,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>15</v>
@@ -2183,10 +2183,10 @@
         <v>17</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>19</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>15</v>
@@ -2227,10 +2227,10 @@
         <v>17</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>19</v>
@@ -2259,7 +2259,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>15</v>
@@ -2271,10 +2271,10 @@
         <v>17</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>19</v>
@@ -2303,7 +2303,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>15</v>
@@ -2315,10 +2315,10 @@
         <v>17</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>19</v>
@@ -2347,7 +2347,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>15</v>
@@ -2359,10 +2359,10 @@
         <v>17</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>19</v>
@@ -2391,7 +2391,7 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>15</v>
@@ -2403,10 +2403,10 @@
         <v>17</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>19</v>
@@ -2435,7 +2435,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>15</v>
@@ -2447,10 +2447,10 @@
         <v>17</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>19</v>
@@ -2479,7 +2479,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>15</v>
@@ -2491,10 +2491,10 @@
         <v>17</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>19</v>
@@ -2523,7 +2523,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>15</v>
@@ -2535,10 +2535,10 @@
         <v>17</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>19</v>
@@ -2567,7 +2567,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>15</v>
@@ -2579,10 +2579,10 @@
         <v>17</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>19</v>
@@ -2611,7 +2611,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>15</v>
@@ -2623,10 +2623,10 @@
         <v>17</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>19</v>
@@ -2655,22 +2655,22 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>32</v>
@@ -2699,7 +2699,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>15</v>
@@ -2711,10 +2711,10 @@
         <v>17</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>19</v>
@@ -2743,7 +2743,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>15</v>
@@ -2755,10 +2755,10 @@
         <v>17</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>19</v>
@@ -2787,7 +2787,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>15</v>
@@ -2799,10 +2799,10 @@
         <v>17</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>19</v>
@@ -2831,22 +2831,22 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>32</v>
@@ -2875,7 +2875,7 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>15</v>
@@ -2887,10 +2887,10 @@
         <v>17</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>19</v>
@@ -2911,7 +2911,7 @@
         <v>35</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N42" s="2" t="s">
         <v>17</v>
@@ -2919,7 +2919,7 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>15</v>
@@ -2931,10 +2931,10 @@
         <v>17</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>32</v>
@@ -2963,22 +2963,22 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>19</v>
@@ -3007,7 +3007,7 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>15</v>
@@ -3019,10 +3019,10 @@
         <v>17</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>19</v>
@@ -3043,7 +3043,7 @@
         <v>35</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N45" s="2" t="s">
         <v>17</v>
@@ -3051,43 +3051,43 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="M46" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J46" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K46" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L46" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M46" s="2" t="s">
-        <v>119</v>
       </c>
       <c r="N46" s="2" t="s">
         <v>17</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>19</v>
@@ -3131,7 +3131,7 @@
         <v>35</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N47" s="2" t="s">
         <v>17</v>
@@ -3139,7 +3139,7 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>15</v>
@@ -3151,10 +3151,10 @@
         <v>17</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>19</v>
@@ -3183,22 +3183,22 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>19</v>
@@ -3227,7 +3227,7 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>15</v>
@@ -3239,10 +3239,10 @@
         <v>17</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>19</v>
@@ -3260,7 +3260,7 @@
         <v>17</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M50" s="2" t="s">
         <v>27</v>
@@ -3271,7 +3271,7 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>15</v>
@@ -3283,10 +3283,10 @@
         <v>17</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>19</v>
@@ -3304,7 +3304,7 @@
         <v>17</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M51" s="2" t="s">
         <v>27</v>
@@ -3315,22 +3315,22 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>32</v>
@@ -3359,7 +3359,7 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>15</v>
@@ -3371,22 +3371,22 @@
         <v>57</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K53" s="2" t="s">
         <v>17</v>
@@ -3395,15 +3395,15 @@
         <v>35</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>15</v>
@@ -3415,10 +3415,10 @@
         <v>17</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>32</v>
@@ -3447,7 +3447,7 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>15</v>
@@ -3459,10 +3459,10 @@
         <v>17</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>19</v>
@@ -3491,7 +3491,7 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>15</v>
@@ -3503,10 +3503,10 @@
         <v>17</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>19</v>
@@ -3535,7 +3535,7 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>15</v>
@@ -3547,10 +3547,10 @@
         <v>17</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>19</v>
@@ -3591,7 +3591,7 @@
         <v>57</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>59</v>
@@ -3609,16 +3609,16 @@
         <v>62</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="L58" s="2" t="s">
         <v>35</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
@@ -3629,13 +3629,13 @@
         <v>15</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>57</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>59</v>
@@ -3653,51 +3653,51 @@
         <v>62</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>35</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>57</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L60" s="2" t="s">
         <v>35</v>
@@ -3706,12 +3706,12 @@
         <v>21</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>15</v>
@@ -3723,10 +3723,10 @@
         <v>17</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>19</v>
@@ -3755,7 +3755,7 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>15</v>
@@ -3767,10 +3767,10 @@
         <v>17</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>19</v>
@@ -3799,7 +3799,7 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>15</v>
@@ -3811,10 +3811,10 @@
         <v>17</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>19</v>
@@ -3843,7 +3843,7 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>15</v>
@@ -3855,10 +3855,10 @@
         <v>17</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>19</v>
@@ -3887,7 +3887,7 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>15</v>
@@ -3899,10 +3899,10 @@
         <v>17</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>19</v>
@@ -3931,22 +3931,22 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>19</v>
@@ -3975,7 +3975,7 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>15</v>
@@ -3987,10 +3987,10 @@
         <v>17</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>19</v>
@@ -4011,7 +4011,7 @@
         <v>20</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N67" s="2" t="s">
         <v>17</v>
@@ -4019,7 +4019,7 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>15</v>
@@ -4031,10 +4031,10 @@
         <v>17</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>19</v>
@@ -4055,7 +4055,7 @@
         <v>35</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N68" s="2" t="s">
         <v>17</v>
@@ -4063,7 +4063,7 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>15</v>
@@ -4075,10 +4075,10 @@
         <v>17</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>19</v>
@@ -4099,7 +4099,7 @@
         <v>35</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N69" s="2" t="s">
         <v>17</v>
@@ -4107,7 +4107,7 @@
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>15</v>
@@ -4119,10 +4119,10 @@
         <v>17</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>19</v>
@@ -4143,7 +4143,7 @@
         <v>35</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N70" s="2" t="s">
         <v>17</v>
@@ -4151,7 +4151,7 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>15</v>
@@ -4163,10 +4163,10 @@
         <v>17</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>19</v>
@@ -4187,7 +4187,7 @@
         <v>35</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N71" s="2" t="s">
         <v>17</v>
@@ -4195,7 +4195,7 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>15</v>
@@ -4207,10 +4207,10 @@
         <v>17</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>19</v>
@@ -4228,10 +4228,10 @@
         <v>17</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N72" s="2" t="s">
         <v>17</v>
@@ -4239,7 +4239,7 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>15</v>
@@ -4251,10 +4251,10 @@
         <v>17</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>19</v>
@@ -4275,7 +4275,7 @@
         <v>35</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N73" s="2" t="s">
         <v>17</v>
@@ -4283,7 +4283,7 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>15</v>
@@ -4295,10 +4295,10 @@
         <v>17</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>19</v>
@@ -4319,7 +4319,7 @@
         <v>35</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N74" s="2" t="s">
         <v>17</v>
@@ -4327,7 +4327,7 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>15</v>
@@ -4339,10 +4339,10 @@
         <v>17</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>19</v>
@@ -4360,10 +4360,10 @@
         <v>17</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N75" s="2" t="s">
         <v>17</v>
@@ -4371,7 +4371,7 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>15</v>
@@ -4383,10 +4383,10 @@
         <v>17</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>19</v>
@@ -4404,10 +4404,10 @@
         <v>17</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N76" s="2" t="s">
         <v>17</v>
@@ -4426,23 +4426,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -4450,16 +4450,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -4478,7 +4478,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -4499,7 +4499,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -4530,12 +4530,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B2">
         <v>75</v>
@@ -4559,25 +4559,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -4594,13 +4594,13 @@
         <v>65</v>
       </c>
       <c r="G10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -4612,7 +4612,7 @@
         <v>62</v>
       </c>
       <c r="P10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q10">
         <v>10</v>
@@ -4620,7 +4620,7 @@
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E11">
         <v>5</v>
@@ -4632,7 +4632,7 @@
         <v>10</v>
       </c>
       <c r="J11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K11">
         <v>75</v>
@@ -4644,15 +4644,15 @@
         <v>3</v>
       </c>
       <c r="P11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q11">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E12">
         <v>4</v>
@@ -4664,7 +4664,7 @@
         <v>65</v>
       </c>
       <c r="M12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N12">
         <v>1</v>
@@ -4673,24 +4673,24 @@
         <v>21</v>
       </c>
       <c r="Q12">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N13">
         <v>4</v>
@@ -4699,12 +4699,12 @@
         <v>27</v>
       </c>
       <c r="Q13">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="7:17" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -4714,12 +4714,6 @@
       </c>
       <c r="N14">
         <v>5</v>
-      </c>
-      <c r="P14" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q14">
-        <v>1</v>
       </c>
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
@@ -4767,30 +4761,30 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>56</v>
+        <v>137</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>58</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4801,10 +4795,10 @@
         <v>15</v>
       </c>
       <c r="F23" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>149</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4815,7 +4809,7 @@
         <v>15</v>
       </c>
       <c r="F24" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>150</v>
@@ -4823,16 +4817,16 @@
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>136</v>
+        <v>56</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F25" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">

--- a/utils/monday_sprint_sprint_2025-5.xlsx
+++ b/utils/monday_sprint_sprint_2025-5.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="247">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>30173</t>
+    <t>8539924492</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>21/02/2025</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>09/03/2025</t>
   </si>
   <si>
     <t>Implantação</t>
@@ -102,19 +102,19 @@
     <t>Fevereiro</t>
   </si>
   <si>
-    <t>30081</t>
+    <t>8540309646</t>
   </si>
   <si>
     <t>INVENTÁRIO WMS</t>
   </si>
   <si>
+    <t>23/02/2025</t>
+  </si>
+  <si>
     <t>A fazer</t>
   </si>
   <si>
-    <t>Aberto</t>
-  </si>
-  <si>
-    <t>29476</t>
+    <t>8550229207</t>
   </si>
   <si>
     <t>Qlik Sense - Dados Parcelas Invoice e Pgto</t>
@@ -126,13 +126,13 @@
     <t>Semana 4</t>
   </si>
   <si>
-    <t>30088</t>
+    <t>8540270328</t>
   </si>
   <si>
     <t>Alteração MOL-340 APP de CHECKLIST</t>
   </si>
   <si>
-    <t>29599</t>
+    <t>8550236147</t>
   </si>
   <si>
     <t>Relatório de Contas a receber - Gerencial no SENSE</t>
@@ -141,22 +141,28 @@
     <t>Alta</t>
   </si>
   <si>
-    <t>29678</t>
+    <t>05/03/2025</t>
+  </si>
+  <si>
+    <t>8550229375</t>
   </si>
   <si>
     <t>Qlik Sense - Base do Recibo de Embarque e Tickets</t>
   </si>
   <si>
+    <t>10/03/2025</t>
+  </si>
+  <si>
     <t>Feito</t>
   </si>
   <si>
-    <t>29477</t>
+    <t>8550239269</t>
   </si>
   <si>
     <t>Qlik Sense - Custos de Exportação "ID"</t>
   </si>
   <si>
-    <t>30218</t>
+    <t>8561200061</t>
   </si>
   <si>
     <t>Altona || Sistema ERP || Devolução de compra - Centro de Custo</t>
@@ -174,19 +180,22 @@
     <t>27/02/2025</t>
   </si>
   <si>
-    <t>30111</t>
+    <t>8540175869</t>
   </si>
   <si>
     <t>ACESSO AO GED NO ALERTA DE REVISÃO AC</t>
   </si>
   <si>
-    <t>29221</t>
+    <t>8550880434</t>
   </si>
   <si>
     <t>Alteração do sistema SMI</t>
   </si>
   <si>
-    <t>29191</t>
+    <t>06/03/2025</t>
+  </si>
+  <si>
+    <t>8092788008</t>
   </si>
   <si>
     <t>Painel - controle de terceirizações</t>
@@ -195,28 +204,31 @@
     <t>20/12/2024</t>
   </si>
   <si>
+    <t>03/03/2025</t>
+  </si>
+  <si>
     <t>Dezembro</t>
   </si>
   <si>
-    <t>29489</t>
+    <t>8537114226</t>
   </si>
   <si>
     <t>Atualização do sistema CPC/OTF</t>
   </si>
   <si>
-    <t>30208</t>
+    <t>8539673664</t>
   </si>
   <si>
     <t>APONTAMENTOS TABLET MANIPULADORES</t>
   </si>
   <si>
-    <t>30223</t>
+    <t>8540624288</t>
   </si>
   <si>
     <t>Alteração do P Number Cliente Solar</t>
   </si>
   <si>
-    <t>30186</t>
+    <t>8539818173</t>
   </si>
   <si>
     <t>Códigos de parada HS500</t>
@@ -225,6 +237,9 @@
     <t>30012</t>
   </si>
   <si>
+    <t>PCP</t>
+  </si>
+  <si>
     <t>Solicitação de serviço</t>
   </si>
   <si>
@@ -243,13 +258,13 @@
     <t>19/05/2026</t>
   </si>
   <si>
-    <t>30225</t>
+    <t>8540606902</t>
   </si>
   <si>
     <t>ADICIONAR MOTIVO DE PARADA 'AGUARDANDO TOMBAMENTO DE PEÇA' -</t>
   </si>
   <si>
-    <t>29333</t>
+    <t>8441951637</t>
   </si>
   <si>
     <t>Conferencia de nota fiscal - almoxarifado</t>
@@ -261,100 +276,103 @@
     <t>Semana 2</t>
   </si>
   <si>
-    <t>30107</t>
+    <t>8540207684</t>
   </si>
   <si>
     <t>Gestão de Terceiros</t>
   </si>
   <si>
-    <t>30096</t>
+    <t>8540242894</t>
   </si>
   <si>
     <t>Altona || Sistema ERP || Relatório Consignados</t>
   </si>
   <si>
-    <t>30194</t>
-  </si>
-  <si>
-    <t>30095</t>
+    <t>8539803288</t>
+  </si>
+  <si>
+    <t>8540258339</t>
   </si>
   <si>
     <t>PARADAS ELETRONICAS MANIPULADORES</t>
   </si>
   <si>
-    <t>30157</t>
+    <t>8539951371</t>
   </si>
   <si>
     <t>Acionamento - Chamado por QR Cod</t>
   </si>
   <si>
-    <t>30070</t>
+    <t>8540348759</t>
   </si>
   <si>
     <t>P Number Solar</t>
   </si>
   <si>
-    <t>29995</t>
+    <t>8540520149</t>
   </si>
   <si>
     <t>Liberação de Ordens.</t>
   </si>
   <si>
-    <t>30155</t>
+    <t>8539963491</t>
   </si>
   <si>
     <t>Sistema de chamado - WMS</t>
   </si>
   <si>
-    <t>30145</t>
+    <t>8540079990</t>
   </si>
   <si>
     <t>Sistema de modelos</t>
   </si>
   <si>
-    <t>30036</t>
+    <t>8540469548</t>
   </si>
   <si>
     <t>inclusão de não conformidades</t>
   </si>
   <si>
-    <t>30052</t>
+    <t>8540449927</t>
   </si>
   <si>
     <t>VOLTAR PARA CONFERENCIA DE NOTA FISCAL</t>
   </si>
   <si>
-    <t>30031</t>
+    <t>8540487111</t>
   </si>
   <si>
     <t>Abertura de SS</t>
   </si>
   <si>
-    <t>30136</t>
+    <t>8540111510</t>
   </si>
   <si>
     <t>ACRESCENTAR MOTIVO DE PARADA - CONFERÊNCIA/ EVIDÊNCIAS DE DIÂMETRO USINADO.</t>
   </si>
   <si>
-    <t>30201</t>
+    <t>8539691721</t>
   </si>
   <si>
     <t>MUDAR COLUNA DE LUGAR</t>
   </si>
   <si>
-    <t>30065</t>
+    <t>04/03/2025</t>
+  </si>
+  <si>
+    <t>8540412609</t>
   </si>
   <si>
     <t>ALTERAÇÃO NOMES DE SETORES</t>
   </si>
   <si>
-    <t>22124</t>
+    <t>8550830050</t>
   </si>
   <si>
     <t>Alteração de condição do sistema de mantuenção</t>
   </si>
   <si>
-    <t>29930</t>
+    <t>8550281795</t>
   </si>
   <si>
     <t>Correção</t>
@@ -363,25 +381,25 @@
     <t>ERRO: Sistema Apontamentos Tratamento Térmico (Revisão ticket 26785) (copy)</t>
   </si>
   <si>
-    <t>30183</t>
+    <t>8539881570</t>
   </si>
   <si>
     <t>Vinculação cBenef</t>
   </si>
   <si>
-    <t>30109</t>
+    <t>8540193190</t>
   </si>
   <si>
     <t>Inventário - WMS</t>
   </si>
   <si>
-    <t>30080</t>
+    <t>8540325532</t>
   </si>
   <si>
     <t>Criar operação de apontamento nova</t>
   </si>
   <si>
-    <t>27180</t>
+    <t>8572195320</t>
   </si>
   <si>
     <t>Ajustes IROG inspeção</t>
@@ -390,7 +408,10 @@
     <t>26/02/2025</t>
   </si>
   <si>
-    <t>29734</t>
+    <t>08/03/2025</t>
+  </si>
+  <si>
+    <t>8438449269</t>
   </si>
   <si>
     <t>DESENVOLVIMENTO DO SISTEMA DE POSTO DE CÓPIAS ELETRÔNICO</t>
@@ -399,13 +420,13 @@
     <t>09/02/2025</t>
   </si>
   <si>
-    <t>28708</t>
+    <t>8584257165</t>
   </si>
   <si>
     <t>Ajuste no sistema BLOCO K</t>
   </si>
   <si>
-    <t>30309</t>
+    <t>8592236046</t>
   </si>
   <si>
     <t>Erro ao acessar o relatório de estatísticas de movimentação no sistema de PCP</t>
@@ -414,31 +435,25 @@
     <t>28/02/2025</t>
   </si>
   <si>
-    <t>30249</t>
+    <t>8618412200</t>
   </si>
   <si>
     <t>Relatório de Seq. Sem Atividade Complementar</t>
   </si>
   <si>
-    <t>04/03/2025</t>
-  </si>
-  <si>
     <t>Semana 1</t>
   </si>
   <si>
     <t>Março</t>
   </si>
   <si>
-    <t>30390</t>
+    <t>8627781359</t>
   </si>
   <si>
     <t>Problemas com Vencimento entre Ordem de Compra e Benner</t>
   </si>
   <si>
-    <t>05/03/2025</t>
-  </si>
-  <si>
-    <t>30349</t>
+    <t>8647240025</t>
   </si>
   <si>
     <t>Movimentação retroativa - 5530</t>
@@ -447,7 +462,7 @@
     <t>07/03/2025</t>
   </si>
   <si>
-    <t>29686</t>
+    <t>8327450541</t>
   </si>
   <si>
     <t>Apontamentos digital jatos</t>
@@ -459,7 +474,7 @@
     <t>Janeiro</t>
   </si>
   <si>
-    <t>25807</t>
+    <t>8547470329</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -468,10 +483,7 @@
     <t>Previsao de vendas</t>
   </si>
   <si>
-    <t>23/02/2025</t>
-  </si>
-  <si>
-    <t>28956</t>
+    <t>8550145476</t>
   </si>
   <si>
     <t>Movimentar sequencia para pendencia de qualidade (setor: 5534) quando PDI_RespostaNew.status = "Analisar/avaliar" (atividade depende da publicação do Web service) (copy)</t>
@@ -480,13 +492,16 @@
     <t>Impedimento</t>
   </si>
   <si>
+    <t>8550145497</t>
+  </si>
+  <si>
     <t>Montar relatório de pendências (filtro por status)</t>
   </si>
   <si>
     <t>Fazendo</t>
   </si>
   <si>
-    <t>24746</t>
+    <t>8551177880</t>
   </si>
   <si>
     <t>Atualização das parcelas programadas - Carga do Programado para evento</t>
@@ -495,6 +510,9 @@
     <t>30069</t>
   </si>
   <si>
+    <t>Logística</t>
+  </si>
+  <si>
     <t>Sistema de Controle de Importação</t>
   </si>
   <si>
@@ -507,22 +525,25 @@
     <t>ADH</t>
   </si>
   <si>
-    <t>30238</t>
+    <t>8551225411</t>
   </si>
   <si>
     <t>QVD - Faturamento (Contas a receber)</t>
   </si>
   <si>
-    <t>30087</t>
+    <t>8540291362</t>
   </si>
   <si>
     <t>Ajustes do apontamento individual e registros da USE</t>
   </si>
   <si>
+    <t>8550145507</t>
+  </si>
+  <si>
     <t>Envio automático de alerta para avaliação do analista</t>
   </si>
   <si>
-    <t>29478</t>
+    <t>8550275678</t>
   </si>
   <si>
     <t>Qlik Sense - Custos de Venda Geral (copy)</t>
@@ -537,6 +558,9 @@
     <t>28392</t>
   </si>
   <si>
+    <t>Contabilidade</t>
+  </si>
+  <si>
     <t>Notas de consignado - Medição NIMBI - Geração de OC (WEB)</t>
   </si>
   <si>
@@ -549,21 +573,33 @@
     <t>24/03/2026</t>
   </si>
   <si>
-    <t>23838</t>
+    <t>8584276625</t>
   </si>
   <si>
     <t>Correção dos eventos do workwithplus que não estavam rodando</t>
   </si>
   <si>
+    <t>8584281198</t>
+  </si>
+  <si>
     <t>Alterar o funcionamento do evento ao selecionar um horário no calendário</t>
   </si>
   <si>
+    <t>8584287912</t>
+  </si>
+  <si>
     <t>Gravar a OC e o CNPJ do fornecedor na transação do agendamento (YMS1)</t>
   </si>
   <si>
+    <t>8584293306</t>
+  </si>
+  <si>
     <t>Criar tela para o cadastro de pátio da expedição para coleta</t>
   </si>
   <si>
+    <t>8584295875</t>
+  </si>
+  <si>
     <t>Criar rotina para gerar o calendário do pátio da coleta</t>
   </si>
   <si>
@@ -576,42 +612,63 @@
     <t>Criar base visual do menu superior de modulos</t>
   </si>
   <si>
-    <t>30335</t>
+    <t>8605627196</t>
   </si>
   <si>
     <t>Melhorias apontamento jato</t>
   </si>
   <si>
-    <t>03/03/2025</t>
-  </si>
-  <si>
-    <t>30379</t>
+    <t>8618714082</t>
   </si>
   <si>
     <t>Incluir equipamento na tela de login</t>
   </si>
   <si>
+    <t>8618718564</t>
+  </si>
+  <si>
     <t>Controle de parada e retomada da produção ao clicar no card</t>
   </si>
   <si>
+    <t>8618720649</t>
+  </si>
+  <si>
     <t>Criar tela para apontar paradas e informar motivo</t>
   </si>
   <si>
+    <t>8618724072</t>
+  </si>
+  <si>
     <t>Cadastro de metas por hora (Tabela MDL_MetaHora: | Setor CT00200 |CT00201 | MDL6Turno | MDL6HoraInicio | MDL6HoraFim| MDL6MetaPiso | MDL6MetaVagonete)</t>
   </si>
   <si>
+    <t>8618726465</t>
+  </si>
+  <si>
     <t>Grid com contador de produção de hora em hora, conforme layout atual</t>
   </si>
   <si>
+    <t>8618728785</t>
+  </si>
+  <si>
     <t>Criar registro de apontamento diário na tabeça MDl_TempoSeq ao logar</t>
   </si>
   <si>
+    <t>8618730008</t>
+  </si>
+  <si>
     <t>Criar grid de paradas</t>
   </si>
   <si>
+    <t>8618731881</t>
+  </si>
+  <si>
     <t>Informar quantidade produzida por hora  (piso e vagonete)</t>
   </si>
   <si>
+    <t>8618733681</t>
+  </si>
+  <si>
     <t>Atualizar card de produção diária</t>
   </si>
   <si>
@@ -621,7 +678,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2025-5</t>
+    <t>Dez/2024</t>
   </si>
   <si>
     <t>Base</t>
@@ -1257,13 +1314,13 @@
         <v>23</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>27</v>
@@ -1351,13 +1408,13 @@
         <v>23</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>27</v>
@@ -1398,7 +1455,7 @@
         <v>35</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>25</v>
@@ -1415,7 +1472,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1427,10 +1484,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
@@ -1445,10 +1502,10 @@
         <v>35</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>26</v>
@@ -1462,7 +1519,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1474,10 +1531,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>20</v>
@@ -1492,10 +1549,10 @@
         <v>35</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>26</v>
@@ -1509,7 +1566,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1521,10 +1578,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>20</v>
@@ -1536,16 +1593,16 @@
         <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>36</v>
@@ -1556,7 +1613,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1568,10 +1625,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
@@ -1583,13 +1640,13 @@
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M10" s="2" t="s">
         <v>26</v>
@@ -1603,7 +1660,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1615,10 +1672,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
@@ -1633,10 +1690,10 @@
         <v>23</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M11" s="2" t="s">
         <v>26</v>
@@ -1650,7 +1707,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1662,10 +1719,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
@@ -1680,10 +1737,10 @@
         <v>35</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M12" s="2" t="s">
         <v>26</v>
@@ -1697,7 +1754,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1709,10 +1766,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
@@ -1724,13 +1781,13 @@
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M13" s="2" t="s">
         <v>26</v>
@@ -1739,12 +1796,12 @@
         <v>27</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1756,10 +1813,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1774,10 +1831,10 @@
         <v>23</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M14" s="2" t="s">
         <v>26</v>
@@ -1791,7 +1848,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1803,10 +1860,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1824,7 +1881,7 @@
         <v>24</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M15" s="2" t="s">
         <v>26</v>
@@ -1838,7 +1895,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1850,10 +1907,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -1868,10 +1925,10 @@
         <v>23</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M16" s="2" t="s">
         <v>26</v>
@@ -1885,7 +1942,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1897,10 +1954,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -1915,10 +1972,10 @@
         <v>23</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M17" s="2" t="s">
         <v>26</v>
@@ -1932,40 +1989,40 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>41</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>35</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M18" s="2" t="s">
         <v>26</v>
@@ -1979,7 +2036,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1991,10 +2048,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -2009,10 +2066,10 @@
         <v>23</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M19" s="2" t="s">
         <v>26</v>
@@ -2026,7 +2083,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -2038,10 +2095,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -2053,19 +2110,19 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>28</v>
@@ -2073,7 +2130,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -2085,10 +2142,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
@@ -2106,7 +2163,7 @@
         <v>24</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>26</v>
@@ -2120,7 +2177,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -2132,10 +2189,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -2150,10 +2207,10 @@
         <v>23</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>26</v>
@@ -2167,7 +2224,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -2179,10 +2236,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -2197,10 +2254,10 @@
         <v>23</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M23" s="2" t="s">
         <v>26</v>
@@ -2214,7 +2271,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -2226,10 +2283,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -2244,10 +2301,10 @@
         <v>23</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M24" s="2" t="s">
         <v>26</v>
@@ -2261,7 +2318,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2273,10 +2330,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
@@ -2294,7 +2351,7 @@
         <v>24</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M25" s="2" t="s">
         <v>26</v>
@@ -2308,7 +2365,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2320,10 +2377,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -2338,10 +2395,10 @@
         <v>23</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M26" s="2" t="s">
         <v>26</v>
@@ -2355,7 +2412,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2367,10 +2424,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2388,7 +2445,7 @@
         <v>24</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M27" s="2" t="s">
         <v>26</v>
@@ -2402,7 +2459,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2414,10 +2471,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
@@ -2435,7 +2492,7 @@
         <v>24</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M28" s="2" t="s">
         <v>26</v>
@@ -2449,7 +2506,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2461,10 +2518,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2479,10 +2536,10 @@
         <v>23</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M29" s="2" t="s">
         <v>26</v>
@@ -2496,7 +2553,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2508,10 +2565,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
@@ -2526,10 +2583,10 @@
         <v>23</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M30" s="2" t="s">
         <v>26</v>
@@ -2543,7 +2600,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2555,10 +2612,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -2573,10 +2630,10 @@
         <v>23</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M31" s="2" t="s">
         <v>26</v>
@@ -2590,7 +2647,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2602,10 +2659,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>20</v>
@@ -2620,10 +2677,10 @@
         <v>23</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M32" s="2" t="s">
         <v>26</v>
@@ -2637,7 +2694,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2649,10 +2706,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
@@ -2667,10 +2724,10 @@
         <v>23</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M33" s="2" t="s">
         <v>26</v>
@@ -2684,7 +2741,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
@@ -2696,10 +2753,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>20</v>
@@ -2714,10 +2771,10 @@
         <v>23</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M34" s="2" t="s">
         <v>26</v>
@@ -2731,7 +2788,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2743,10 +2800,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
@@ -2761,10 +2818,10 @@
         <v>23</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M35" s="2" t="s">
         <v>26</v>
@@ -2778,7 +2835,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -2790,10 +2847,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
@@ -2808,10 +2865,10 @@
         <v>35</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M36" s="2" t="s">
         <v>26</v>
@@ -2825,22 +2882,22 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>41</v>
@@ -2858,7 +2915,7 @@
         <v>24</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M37" s="2" t="s">
         <v>26</v>
@@ -2872,7 +2929,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
@@ -2884,10 +2941,10 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>20</v>
@@ -2902,10 +2959,10 @@
         <v>23</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M38" s="2" t="s">
         <v>26</v>
@@ -2919,7 +2976,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
@@ -2931,10 +2988,10 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>20</v>
@@ -2952,7 +3009,7 @@
         <v>24</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M39" s="2" t="s">
         <v>26</v>
@@ -2966,7 +3023,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
@@ -2978,10 +3035,10 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>20</v>
@@ -2996,10 +3053,10 @@
         <v>23</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M40" s="2" t="s">
         <v>26</v>
@@ -3013,22 +3070,22 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>41</v>
@@ -3040,13 +3097,13 @@
         <v>22</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>131</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M41" s="2" t="s">
         <v>26</v>
@@ -3060,7 +3117,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
@@ -3072,10 +3129,10 @@
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>20</v>
@@ -3087,19 +3144,19 @@
         <v>22</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M42" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="O42" s="2" t="s">
         <v>28</v>
@@ -3107,7 +3164,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
@@ -3119,10 +3176,10 @@
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>41</v>
@@ -3134,13 +3191,13 @@
         <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>24</v>
+        <v>130</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M43" s="2" t="s">
         <v>26</v>
@@ -3154,40 +3211,40 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="K44" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="F44" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J44" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="K44" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="L44" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M44" s="2" t="s">
         <v>26</v>
@@ -3201,7 +3258,7 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>16</v>
@@ -3213,10 +3270,10 @@
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>20</v>
@@ -3228,121 +3285,121 @@
         <v>22</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>24</v>
+        <v>131</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M45" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C46" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K46" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D46" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J46" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="K46" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="L46" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M46" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N47" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="F47" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J47" s="2" t="s">
+      <c r="O47" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="K47" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L47" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M47" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N47" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="O47" s="2" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>16</v>
@@ -3354,10 +3411,10 @@
         <v>18</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>20</v>
@@ -3369,10 +3426,10 @@
         <v>22</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>25</v>
@@ -3384,27 +3441,27 @@
         <v>36</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>20</v>
@@ -3416,13 +3473,13 @@
         <v>22</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>151</v>
+        <v>31</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M49" s="2" t="s">
         <v>26</v>
@@ -3436,7 +3493,7 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>16</v>
@@ -3448,10 +3505,10 @@
         <v>18</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>20</v>
@@ -3466,13 +3523,13 @@
         <v>35</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N50" s="2" t="s">
         <v>36</v>
@@ -3483,7 +3540,7 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>16</v>
@@ -3495,10 +3552,10 @@
         <v>18</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>20</v>
@@ -3513,13 +3570,13 @@
         <v>35</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N51" s="2" t="s">
         <v>36</v>
@@ -3530,22 +3587,22 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>41</v>
@@ -3563,7 +3620,7 @@
         <v>24</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M52" s="2" t="s">
         <v>26</v>
@@ -3577,31 +3634,31 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>16</v>
+        <v>165</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>23</v>
@@ -3610,7 +3667,7 @@
         <v>24</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M53" s="2" t="s">
         <v>26</v>
@@ -3624,7 +3681,7 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>16</v>
@@ -3636,10 +3693,10 @@
         <v>18</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>41</v>
@@ -3654,10 +3711,10 @@
         <v>35</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M54" s="2" t="s">
         <v>26</v>
@@ -3671,7 +3728,7 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>16</v>
@@ -3683,10 +3740,10 @@
         <v>18</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>20</v>
@@ -3704,7 +3761,7 @@
         <v>24</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M55" s="2" t="s">
         <v>26</v>
@@ -3718,7 +3775,7 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>16</v>
@@ -3730,10 +3787,10 @@
         <v>18</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>20</v>
@@ -3748,10 +3805,10 @@
         <v>35</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M56" s="2" t="s">
         <v>26</v>
@@ -3765,7 +3822,7 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>16</v>
@@ -3777,10 +3834,10 @@
         <v>18</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>20</v>
@@ -3798,7 +3855,7 @@
         <v>24</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M57" s="2" t="s">
         <v>26</v>
@@ -3812,40 +3869,40 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>41</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>35</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M58" s="2" t="s">
         <v>26</v>
@@ -3859,40 +3916,40 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>41</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M59" s="2" t="s">
         <v>26</v>
@@ -3906,46 +3963,46 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>16</v>
+        <v>181</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>41</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M60" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="O60" s="2" t="s">
         <v>28</v>
@@ -3953,7 +4010,7 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>16</v>
@@ -3965,10 +4022,10 @@
         <v>18</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>20</v>
@@ -3980,13 +4037,13 @@
         <v>22</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M61" s="2" t="s">
         <v>26</v>
@@ -4000,7 +4057,7 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>16</v>
@@ -4012,10 +4069,10 @@
         <v>18</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>20</v>
@@ -4027,13 +4084,13 @@
         <v>22</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M62" s="2" t="s">
         <v>26</v>
@@ -4047,7 +4104,7 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>16</v>
@@ -4059,10 +4116,10 @@
         <v>18</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>20</v>
@@ -4074,13 +4131,13 @@
         <v>22</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M63" s="2" t="s">
         <v>26</v>
@@ -4094,7 +4151,7 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>16</v>
@@ -4106,10 +4163,10 @@
         <v>18</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>20</v>
@@ -4121,13 +4178,13 @@
         <v>22</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M64" s="2" t="s">
         <v>26</v>
@@ -4141,7 +4198,7 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>16</v>
@@ -4153,10 +4210,10 @@
         <v>18</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>20</v>
@@ -4168,13 +4225,13 @@
         <v>22</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>24</v>
+        <v>131</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M65" s="2" t="s">
         <v>26</v>
@@ -4188,22 +4245,22 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>20</v>
@@ -4215,13 +4272,13 @@
         <v>22</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>24</v>
+        <v>130</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M66" s="2" t="s">
         <v>26</v>
@@ -4235,7 +4292,7 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>16</v>
@@ -4247,10 +4304,10 @@
         <v>18</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>20</v>
@@ -4262,10 +4319,10 @@
         <v>22</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>189</v>
+        <v>63</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>25</v>
@@ -4274,15 +4331,15 @@
         <v>26</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>16</v>
@@ -4294,10 +4351,10 @@
         <v>18</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>20</v>
@@ -4309,27 +4366,27 @@
         <v>22</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M68" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="O68" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>16</v>
@@ -4341,10 +4398,10 @@
         <v>18</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>20</v>
@@ -4356,27 +4413,27 @@
         <v>22</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M69" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="O69" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>16</v>
@@ -4388,10 +4445,10 @@
         <v>18</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>20</v>
@@ -4403,27 +4460,27 @@
         <v>22</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M70" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>16</v>
@@ -4435,10 +4492,10 @@
         <v>18</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>20</v>
@@ -4450,27 +4507,27 @@
         <v>22</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M71" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="O71" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>16</v>
@@ -4482,10 +4539,10 @@
         <v>18</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>20</v>
@@ -4497,27 +4554,27 @@
         <v>22</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="O72" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>16</v>
@@ -4529,10 +4586,10 @@
         <v>18</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>20</v>
@@ -4544,27 +4601,27 @@
         <v>22</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M73" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="O73" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>16</v>
@@ -4576,10 +4633,10 @@
         <v>18</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>20</v>
@@ -4591,27 +4648,27 @@
         <v>22</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M74" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="O74" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>16</v>
@@ -4623,10 +4680,10 @@
         <v>18</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>20</v>
@@ -4638,27 +4695,27 @@
         <v>22</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="O75" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>190</v>
+        <v>217</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>16</v>
@@ -4670,10 +4727,10 @@
         <v>18</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>20</v>
@@ -4685,22 +4742,22 @@
         <v>22</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="O76" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -4716,23 +4773,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="B2" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="D2" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="E2" t="s">
-        <v>204</v>
+        <v>223</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -4740,16 +4797,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -4760,20 +4817,20 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>438.75</v>
+        <v>35.61</v>
       </c>
       <c r="J5" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J22" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K22">
         <v>62</v>
@@ -4789,7 +4846,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -4820,12 +4877,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="B2">
         <v>75</v>
@@ -4839,35 +4896,35 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>438.75</v>
+        <v>35.61</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -4875,7 +4932,7 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
@@ -4884,33 +4941,39 @@
         <v>65</v>
       </c>
       <c r="G10" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N10">
         <v>62</v>
       </c>
       <c r="P10" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="Q10">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="4:17" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11">
+        <v>3</v>
+      </c>
       <c r="D11" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E11">
         <v>5</v>
@@ -4925,24 +4988,30 @@
         <v>26</v>
       </c>
       <c r="K11">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="M11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N11">
         <v>3</v>
       </c>
       <c r="P11" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="Q11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="4:17" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>165</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
       <c r="D12" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E12">
         <v>4</v>
@@ -4954,13 +5023,13 @@
         <v>65</v>
       </c>
       <c r="J12" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="K12">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="N12">
         <v>1</v>
@@ -4969,24 +5038,30 @@
         <v>27</v>
       </c>
       <c r="Q12">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="4:17" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>181</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
       <c r="D13" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="N13">
         <v>4</v>
@@ -4995,12 +5070,12 @@
         <v>36</v>
       </c>
       <c r="Q13">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -5014,7 +5089,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -5022,7 +5097,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -5030,7 +5105,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -5038,10 +5113,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -5049,7 +5124,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -5057,142 +5132,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>435</v>
+        <v>530</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>435</v>
+        <v>530</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>171</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>432</v>
+        <v>530</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>172</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>393</v>
+        <v>530</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>15</v>
+        <v>159</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>530</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>19</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>33</v>
+        <v>209</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>530</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>39</v>
+        <v>215</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>530</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>40</v>
+        <v>216</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>42</v>
+        <v>217</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>530</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>43</v>
+        <v>218</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>51</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
